--- a/sku_mapping.xlsx
+++ b/sku_mapping.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="124">
   <si>
     <t>原始SKU</t>
   </si>
@@ -346,10 +346,22 @@
     <t>009-192-14B</t>
   </si>
   <si>
-    <t>006-137-12G</t>
-  </si>
-  <si>
-    <t>008-137-12G</t>
+    <t>WS008-152-12C</t>
+  </si>
+  <si>
+    <t>WS008-192-12C</t>
+  </si>
+  <si>
+    <t>WS008-137-12C</t>
+  </si>
+  <si>
+    <t>008-152-12-1</t>
+  </si>
+  <si>
+    <t>008-192-12-1</t>
+  </si>
+  <si>
+    <t>L8-137-12</t>
   </si>
   <si>
     <t>WS007-30-TWIN</t>
@@ -705,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B111"/>
+  <dimension ref="A1:B115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -721,7 +733,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -729,7 +741,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -737,7 +749,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -745,7 +757,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -753,7 +765,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -761,7 +773,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -769,7 +781,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -777,7 +789,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -785,7 +797,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -793,7 +805,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -801,7 +813,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -809,7 +821,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -817,7 +829,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -825,7 +837,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -833,7 +845,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -841,7 +853,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -849,7 +861,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -857,7 +869,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -865,7 +877,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -873,7 +885,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -881,7 +893,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -889,7 +901,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -897,7 +909,7 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -905,7 +917,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -913,7 +925,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -921,7 +933,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -929,7 +941,7 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -937,7 +949,7 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -945,7 +957,7 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -953,7 +965,7 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -961,7 +973,7 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -969,7 +981,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1585,7 +1597,7 @@
         <v>110</v>
       </c>
       <c r="B110" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1593,7 +1605,39 @@
         <v>111</v>
       </c>
       <c r="B111" t="s">
-        <v>35</v>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" t="s">
+        <v>112</v>
+      </c>
+      <c r="B112" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" t="s">
+        <v>113</v>
+      </c>
+      <c r="B113" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" t="s">
+        <v>114</v>
+      </c>
+      <c r="B114" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" t="s">
+        <v>115</v>
+      </c>
+      <c r="B115" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/sku_mapping.xlsx
+++ b/sku_mapping.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="125">
   <si>
     <t>原始SKU</t>
   </si>
@@ -362,6 +362,9 @@
   </si>
   <si>
     <t>L8-137-12</t>
+  </si>
+  <si>
+    <t>WF-2 008-137-12</t>
   </si>
   <si>
     <t>WS007-30-TWIN</t>
@@ -717,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B115"/>
+  <dimension ref="A1:B116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -733,7 +736,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -741,7 +744,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -749,7 +752,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -757,7 +760,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -765,7 +768,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -773,7 +776,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -781,7 +784,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -789,7 +792,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -797,7 +800,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -805,7 +808,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -813,7 +816,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -821,7 +824,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -829,7 +832,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -837,7 +840,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -845,7 +848,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -853,7 +856,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -861,7 +864,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -869,7 +872,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -877,7 +880,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -885,7 +888,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -893,7 +896,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -901,7 +904,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -909,7 +912,7 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -917,7 +920,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -925,7 +928,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -933,7 +936,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -941,7 +944,7 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -949,7 +952,7 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -957,7 +960,7 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -965,7 +968,7 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -973,7 +976,7 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -981,7 +984,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1637,6 +1640,14 @@
         <v>115</v>
       </c>
       <c r="B115" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" t="s">
+        <v>116</v>
+      </c>
+      <c r="B116" t="s">
         <v>49</v>
       </c>
     </row>

--- a/sku_mapping.xlsx
+++ b/sku_mapping.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="126">
   <si>
     <t>原始SKU</t>
   </si>
@@ -205,7 +205,13 @@
     <t>008-192-14B</t>
   </si>
   <si>
-    <t>L8-137-12</t>
+    <t>WS008-137-12C</t>
+  </si>
+  <si>
+    <t>WS008-152-12C</t>
+  </si>
+  <si>
+    <t>WF-2 008-137-14</t>
   </si>
   <si>
     <t>WF-2 008-137-12</t>
@@ -717,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C111"/>
+  <dimension ref="A1:C113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -736,10 +742,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -747,10 +753,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -758,10 +764,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -769,10 +775,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -780,10 +786,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -791,10 +797,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -802,10 +808,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -813,10 +819,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -824,10 +830,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -835,10 +841,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -846,10 +852,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -857,10 +863,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -868,10 +874,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -879,10 +885,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -890,10 +896,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -901,10 +907,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C17" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -912,10 +918,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -923,10 +929,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -934,10 +940,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -945,10 +951,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -956,10 +962,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C22" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -967,10 +973,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -978,10 +984,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -989,10 +995,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C25" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1000,10 +1006,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1011,10 +1017,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1022,10 +1028,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1033,10 +1039,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1044,10 +1050,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C30" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1055,10 +1061,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1066,10 +1072,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1077,10 +1083,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1091,7 +1097,7 @@
         <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1102,7 +1108,7 @@
         <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1113,7 +1119,7 @@
         <v>37</v>
       </c>
       <c r="C36" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1124,7 +1130,7 @@
         <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1135,7 +1141,7 @@
         <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1146,7 +1152,7 @@
         <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1157,7 +1163,7 @@
         <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1168,7 +1174,7 @@
         <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1179,7 +1185,7 @@
         <v>36</v>
       </c>
       <c r="C42" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1190,7 +1196,7 @@
         <v>37</v>
       </c>
       <c r="C43" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1201,7 +1207,7 @@
         <v>38</v>
       </c>
       <c r="C44" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1212,7 +1218,7 @@
         <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1223,7 +1229,7 @@
         <v>40</v>
       </c>
       <c r="C46" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1234,7 +1240,7 @@
         <v>41</v>
       </c>
       <c r="C47" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1245,7 +1251,7 @@
         <v>35</v>
       </c>
       <c r="C48" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1256,7 +1262,7 @@
         <v>36</v>
       </c>
       <c r="C49" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1267,7 +1273,7 @@
         <v>37</v>
       </c>
       <c r="C50" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1278,7 +1284,7 @@
         <v>38</v>
       </c>
       <c r="C51" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1289,7 +1295,7 @@
         <v>39</v>
       </c>
       <c r="C52" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1300,7 +1306,7 @@
         <v>40</v>
       </c>
       <c r="C53" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1311,7 +1317,7 @@
         <v>41</v>
       </c>
       <c r="C54" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1322,7 +1328,7 @@
         <v>35</v>
       </c>
       <c r="C55" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1333,7 +1339,7 @@
         <v>36</v>
       </c>
       <c r="C56" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1344,7 +1350,7 @@
         <v>37</v>
       </c>
       <c r="C57" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1355,7 +1361,7 @@
         <v>38</v>
       </c>
       <c r="C58" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1366,7 +1372,7 @@
         <v>39</v>
       </c>
       <c r="C59" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1377,7 +1383,7 @@
         <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1388,7 +1394,7 @@
         <v>41</v>
       </c>
       <c r="C61" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1399,7 +1405,7 @@
         <v>36</v>
       </c>
       <c r="C62" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1407,10 +1413,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C63" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1418,10 +1424,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="C64" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1429,10 +1435,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="C65" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1443,7 +1449,7 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1454,7 +1460,7 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1465,7 +1471,7 @@
         <v>81</v>
       </c>
       <c r="C68" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1476,7 +1482,7 @@
         <v>81</v>
       </c>
       <c r="C69" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1487,7 +1493,7 @@
         <v>83</v>
       </c>
       <c r="C70" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1498,7 +1504,7 @@
         <v>83</v>
       </c>
       <c r="C71" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1509,7 +1515,7 @@
         <v>85</v>
       </c>
       <c r="C72" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1520,7 +1526,7 @@
         <v>85</v>
       </c>
       <c r="C73" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1531,7 +1537,7 @@
         <v>87</v>
       </c>
       <c r="C74" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1542,7 +1548,7 @@
         <v>87</v>
       </c>
       <c r="C75" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1550,10 +1556,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C76" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1561,10 +1567,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C77" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1575,7 +1581,7 @@
         <v>79</v>
       </c>
       <c r="C78" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1586,7 +1592,7 @@
         <v>79</v>
       </c>
       <c r="C79" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1597,7 +1603,7 @@
         <v>81</v>
       </c>
       <c r="C80" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1608,7 +1614,7 @@
         <v>81</v>
       </c>
       <c r="C81" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1619,7 +1625,7 @@
         <v>83</v>
       </c>
       <c r="C82" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1630,7 +1636,7 @@
         <v>83</v>
       </c>
       <c r="C83" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1641,7 +1647,7 @@
         <v>85</v>
       </c>
       <c r="C84" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1652,7 +1658,7 @@
         <v>85</v>
       </c>
       <c r="C85" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1663,7 +1669,7 @@
         <v>87</v>
       </c>
       <c r="C86" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1674,7 +1680,7 @@
         <v>87</v>
       </c>
       <c r="C87" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1682,10 +1688,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="C88" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1693,10 +1699,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="C89" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1707,7 +1713,7 @@
         <v>103</v>
       </c>
       <c r="C90" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1718,7 +1724,7 @@
         <v>103</v>
       </c>
       <c r="C91" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1729,7 +1735,7 @@
         <v>105</v>
       </c>
       <c r="C92" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1740,7 +1746,7 @@
         <v>105</v>
       </c>
       <c r="C93" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1751,7 +1757,7 @@
         <v>107</v>
       </c>
       <c r="C94" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1762,7 +1768,7 @@
         <v>107</v>
       </c>
       <c r="C95" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1773,7 +1779,7 @@
         <v>109</v>
       </c>
       <c r="C96" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1784,7 +1790,7 @@
         <v>109</v>
       </c>
       <c r="C97" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1795,7 +1801,7 @@
         <v>111</v>
       </c>
       <c r="C98" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1806,7 +1812,7 @@
         <v>111</v>
       </c>
       <c r="C99" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -1814,10 +1820,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C100" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -1825,10 +1831,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C101" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -1839,7 +1845,7 @@
         <v>103</v>
       </c>
       <c r="C102" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -1850,7 +1856,7 @@
         <v>103</v>
       </c>
       <c r="C103" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -1861,7 +1867,7 @@
         <v>105</v>
       </c>
       <c r="C104" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -1872,7 +1878,7 @@
         <v>105</v>
       </c>
       <c r="C105" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -1883,7 +1889,7 @@
         <v>107</v>
       </c>
       <c r="C106" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -1894,7 +1900,7 @@
         <v>107</v>
       </c>
       <c r="C107" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -1905,7 +1911,7 @@
         <v>109</v>
       </c>
       <c r="C108" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -1916,7 +1922,7 @@
         <v>109</v>
       </c>
       <c r="C109" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -1927,7 +1933,7 @@
         <v>111</v>
       </c>
       <c r="C110" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -1938,7 +1944,29 @@
         <v>111</v>
       </c>
       <c r="C111" t="s">
-        <v>123</v>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
+        <v>113</v>
+      </c>
+      <c r="B112" t="s">
+        <v>113</v>
+      </c>
+      <c r="C112" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" t="s">
+        <v>114</v>
+      </c>
+      <c r="B113" t="s">
+        <v>113</v>
+      </c>
+      <c r="C113" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/sku_mapping.xlsx
+++ b/sku_mapping.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="123">
   <si>
     <t>原始SKU</t>
   </si>
@@ -205,16 +205,7 @@
     <t>008-192-14B</t>
   </si>
   <si>
-    <t>WS008-137-12C</t>
-  </si>
-  <si>
-    <t>WS008-152-12C</t>
-  </si>
-  <si>
-    <t>WF-2 008-137-14</t>
-  </si>
-  <si>
-    <t>WF-2 008-137-12</t>
+    <t>WS008-192-12C</t>
   </si>
   <si>
     <t>WS006-137-12</t>
@@ -723,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C113"/>
+  <dimension ref="A1:C110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -742,10 +733,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -753,10 +744,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -764,10 +755,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -775,10 +766,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -786,10 +777,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -797,10 +788,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -808,10 +799,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -819,10 +810,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -830,10 +821,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -841,10 +832,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -852,10 +843,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C12" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -863,10 +854,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -874,10 +865,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -885,10 +876,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C15" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -896,10 +887,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C16" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -907,10 +898,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -918,10 +909,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C18" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -929,10 +920,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -940,10 +931,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C20" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -951,10 +942,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C21" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -962,10 +953,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -973,10 +964,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C23" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -984,10 +975,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C24" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -995,10 +986,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C25" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1006,10 +997,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1017,10 +1008,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C27" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1028,10 +1019,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C28" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1039,10 +1030,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1050,10 +1041,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1061,10 +1052,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1072,10 +1063,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1083,10 +1074,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1097,7 +1088,7 @@
         <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1108,7 +1099,7 @@
         <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1119,7 +1110,7 @@
         <v>37</v>
       </c>
       <c r="C36" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1130,7 +1121,7 @@
         <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1141,7 +1132,7 @@
         <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1152,7 +1143,7 @@
         <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1163,7 +1154,7 @@
         <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1174,7 +1165,7 @@
         <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1185,7 +1176,7 @@
         <v>36</v>
       </c>
       <c r="C42" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1196,7 +1187,7 @@
         <v>37</v>
       </c>
       <c r="C43" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1207,7 +1198,7 @@
         <v>38</v>
       </c>
       <c r="C44" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1218,7 +1209,7 @@
         <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1229,7 +1220,7 @@
         <v>40</v>
       </c>
       <c r="C46" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1240,7 +1231,7 @@
         <v>41</v>
       </c>
       <c r="C47" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1251,7 +1242,7 @@
         <v>35</v>
       </c>
       <c r="C48" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1262,7 +1253,7 @@
         <v>36</v>
       </c>
       <c r="C49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1273,7 +1264,7 @@
         <v>37</v>
       </c>
       <c r="C50" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1284,7 +1275,7 @@
         <v>38</v>
       </c>
       <c r="C51" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1295,7 +1286,7 @@
         <v>39</v>
       </c>
       <c r="C52" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1306,7 +1297,7 @@
         <v>40</v>
       </c>
       <c r="C53" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1317,7 +1308,7 @@
         <v>41</v>
       </c>
       <c r="C54" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1328,7 +1319,7 @@
         <v>35</v>
       </c>
       <c r="C55" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1339,7 +1330,7 @@
         <v>36</v>
       </c>
       <c r="C56" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1350,7 +1341,7 @@
         <v>37</v>
       </c>
       <c r="C57" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1361,7 +1352,7 @@
         <v>38</v>
       </c>
       <c r="C58" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1372,7 +1363,7 @@
         <v>39</v>
       </c>
       <c r="C59" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1383,7 +1374,7 @@
         <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1394,7 +1385,7 @@
         <v>41</v>
       </c>
       <c r="C61" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1402,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C62" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1413,10 +1404,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="C63" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1424,10 +1415,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="C64" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1435,10 +1426,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1446,10 +1437,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C66" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1457,10 +1448,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C67" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1468,10 +1459,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C68" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1479,10 +1470,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C69" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1490,10 +1481,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C70" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1501,10 +1492,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C71" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1512,10 +1503,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C72" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1523,10 +1514,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C73" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1534,10 +1525,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C74" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1545,10 +1536,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C75" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1556,10 +1547,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C76" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1567,10 +1558,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C77" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1578,10 +1569,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1589,10 +1580,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1600,10 +1591,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1611,10 +1602,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C81" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1622,10 +1613,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C82" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1633,10 +1624,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1644,10 +1635,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C84" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1655,10 +1646,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C85" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1666,10 +1657,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C86" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1677,10 +1668,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C87" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1688,10 +1679,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="C88" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1699,10 +1690,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C89" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1710,10 +1701,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C90" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1721,10 +1712,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C91" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1732,10 +1723,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C92" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1743,10 +1734,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C93" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1754,10 +1745,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C94" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1765,10 +1756,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C95" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1776,10 +1767,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C96" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1787,10 +1778,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C97" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1798,10 +1789,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C98" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1809,10 +1800,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C99" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -1820,10 +1811,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="C100" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -1831,10 +1822,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C101" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -1842,10 +1833,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C102" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -1853,10 +1844,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C103" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -1864,10 +1855,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C104" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -1875,10 +1866,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C105" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -1886,10 +1877,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C106" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -1897,10 +1888,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C107" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -1908,10 +1899,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C108" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -1919,10 +1910,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C109" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -1930,43 +1921,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C110" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111" t="s">
-        <v>112</v>
-      </c>
-      <c r="B111" t="s">
-        <v>111</v>
-      </c>
-      <c r="C111" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3">
-      <c r="A112" t="s">
-        <v>113</v>
-      </c>
-      <c r="B112" t="s">
-        <v>113</v>
-      </c>
-      <c r="C112" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" t="s">
-        <v>114</v>
-      </c>
-      <c r="B113" t="s">
-        <v>113</v>
-      </c>
-      <c r="C113" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/sku_mapping.xlsx
+++ b/sku_mapping.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="125">
   <si>
     <t>原始SKU</t>
   </si>
@@ -206,6 +206,12 @@
   </si>
   <si>
     <t>WS008-192-12C</t>
+  </si>
+  <si>
+    <t>WF-2 008-137-14</t>
+  </si>
+  <si>
+    <t>WS008-137-12C</t>
   </si>
   <si>
     <t>WS006-137-12</t>
@@ -714,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C110"/>
+  <dimension ref="A1:C112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -733,10 +739,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -744,10 +750,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -755,10 +761,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -766,10 +772,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -777,10 +783,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -788,10 +794,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -799,10 +805,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -810,10 +816,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -821,10 +827,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -832,10 +838,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -843,10 +849,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -854,10 +860,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -865,10 +871,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -876,10 +882,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -887,10 +893,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -898,10 +904,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -909,10 +915,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C18" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -920,10 +926,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C19" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -931,10 +937,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -942,10 +948,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -953,10 +959,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -964,10 +970,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -975,10 +981,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -986,10 +992,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -997,10 +1003,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1008,10 +1014,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1019,10 +1025,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1030,10 +1036,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1041,10 +1047,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1052,10 +1058,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1063,10 +1069,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1074,10 +1080,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1088,7 +1094,7 @@
         <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1099,7 +1105,7 @@
         <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1110,7 +1116,7 @@
         <v>37</v>
       </c>
       <c r="C36" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1121,7 +1127,7 @@
         <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1132,7 +1138,7 @@
         <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1143,7 +1149,7 @@
         <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1154,7 +1160,7 @@
         <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1165,7 +1171,7 @@
         <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1176,7 +1182,7 @@
         <v>36</v>
       </c>
       <c r="C42" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1187,7 +1193,7 @@
         <v>37</v>
       </c>
       <c r="C43" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1198,7 +1204,7 @@
         <v>38</v>
       </c>
       <c r="C44" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1209,7 +1215,7 @@
         <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1220,7 +1226,7 @@
         <v>40</v>
       </c>
       <c r="C46" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1231,7 +1237,7 @@
         <v>41</v>
       </c>
       <c r="C47" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1242,7 +1248,7 @@
         <v>35</v>
       </c>
       <c r="C48" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1253,7 +1259,7 @@
         <v>36</v>
       </c>
       <c r="C49" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1264,7 +1270,7 @@
         <v>37</v>
       </c>
       <c r="C50" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1275,7 +1281,7 @@
         <v>38</v>
       </c>
       <c r="C51" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1286,7 +1292,7 @@
         <v>39</v>
       </c>
       <c r="C52" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1297,7 +1303,7 @@
         <v>40</v>
       </c>
       <c r="C53" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1308,7 +1314,7 @@
         <v>41</v>
       </c>
       <c r="C54" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1319,7 +1325,7 @@
         <v>35</v>
       </c>
       <c r="C55" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1330,7 +1336,7 @@
         <v>36</v>
       </c>
       <c r="C56" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1341,7 +1347,7 @@
         <v>37</v>
       </c>
       <c r="C57" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1352,7 +1358,7 @@
         <v>38</v>
       </c>
       <c r="C58" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1363,7 +1369,7 @@
         <v>39</v>
       </c>
       <c r="C59" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1374,7 +1380,7 @@
         <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1385,7 +1391,7 @@
         <v>41</v>
       </c>
       <c r="C61" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1396,7 +1402,7 @@
         <v>40</v>
       </c>
       <c r="C62" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1404,10 +1410,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="C63" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1415,10 +1421,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="C64" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1429,7 +1435,7 @@
         <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1440,7 +1446,7 @@
         <v>78</v>
       </c>
       <c r="C66" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1451,7 +1457,7 @@
         <v>80</v>
       </c>
       <c r="C67" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1462,7 +1468,7 @@
         <v>80</v>
       </c>
       <c r="C68" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1473,7 +1479,7 @@
         <v>82</v>
       </c>
       <c r="C69" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1484,7 +1490,7 @@
         <v>82</v>
       </c>
       <c r="C70" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1495,7 +1501,7 @@
         <v>84</v>
       </c>
       <c r="C71" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1506,7 +1512,7 @@
         <v>84</v>
       </c>
       <c r="C72" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1517,7 +1523,7 @@
         <v>86</v>
       </c>
       <c r="C73" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1528,7 +1534,7 @@
         <v>86</v>
       </c>
       <c r="C74" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1536,10 +1542,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C75" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1547,10 +1553,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C76" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1561,7 +1567,7 @@
         <v>78</v>
       </c>
       <c r="C77" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1572,7 +1578,7 @@
         <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1583,7 +1589,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1594,7 +1600,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1605,7 +1611,7 @@
         <v>82</v>
       </c>
       <c r="C81" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1616,7 +1622,7 @@
         <v>82</v>
       </c>
       <c r="C82" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1627,7 +1633,7 @@
         <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1638,7 +1644,7 @@
         <v>84</v>
       </c>
       <c r="C84" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1649,7 +1655,7 @@
         <v>86</v>
       </c>
       <c r="C85" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1660,7 +1666,7 @@
         <v>86</v>
       </c>
       <c r="C86" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1668,10 +1674,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C87" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1679,10 +1685,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C88" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1693,7 +1699,7 @@
         <v>102</v>
       </c>
       <c r="C89" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1704,7 +1710,7 @@
         <v>102</v>
       </c>
       <c r="C90" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1715,7 +1721,7 @@
         <v>104</v>
       </c>
       <c r="C91" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1726,7 +1732,7 @@
         <v>104</v>
       </c>
       <c r="C92" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1737,7 +1743,7 @@
         <v>106</v>
       </c>
       <c r="C93" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1748,7 +1754,7 @@
         <v>106</v>
       </c>
       <c r="C94" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1759,7 +1765,7 @@
         <v>108</v>
       </c>
       <c r="C95" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1770,7 +1776,7 @@
         <v>108</v>
       </c>
       <c r="C96" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1781,7 +1787,7 @@
         <v>110</v>
       </c>
       <c r="C97" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1792,7 +1798,7 @@
         <v>110</v>
       </c>
       <c r="C98" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1800,10 +1806,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C99" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -1811,10 +1817,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C100" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -1825,7 +1831,7 @@
         <v>102</v>
       </c>
       <c r="C101" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -1836,7 +1842,7 @@
         <v>102</v>
       </c>
       <c r="C102" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -1847,7 +1853,7 @@
         <v>104</v>
       </c>
       <c r="C103" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -1858,7 +1864,7 @@
         <v>104</v>
       </c>
       <c r="C104" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -1869,7 +1875,7 @@
         <v>106</v>
       </c>
       <c r="C105" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -1880,7 +1886,7 @@
         <v>106</v>
       </c>
       <c r="C106" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -1891,7 +1897,7 @@
         <v>108</v>
       </c>
       <c r="C107" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -1902,7 +1908,7 @@
         <v>108</v>
       </c>
       <c r="C108" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -1913,7 +1919,7 @@
         <v>110</v>
       </c>
       <c r="C109" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -1924,7 +1930,29 @@
         <v>110</v>
       </c>
       <c r="C110" t="s">
-        <v>122</v>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" t="s">
+        <v>112</v>
+      </c>
+      <c r="B111" t="s">
+        <v>112</v>
+      </c>
+      <c r="C111" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
+        <v>113</v>
+      </c>
+      <c r="B112" t="s">
+        <v>112</v>
+      </c>
+      <c r="C112" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/sku_mapping.xlsx
+++ b/sku_mapping.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="123">
   <si>
     <t>原始SKU</t>
   </si>
@@ -205,13 +205,7 @@
     <t>008-192-14B</t>
   </si>
   <si>
-    <t>WS008-192-12C</t>
-  </si>
-  <si>
-    <t>WF-2 008-137-14</t>
-  </si>
-  <si>
-    <t>WS008-137-12C</t>
+    <t>WF-2 008-137-12</t>
   </si>
   <si>
     <t>WS006-137-12</t>
@@ -720,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C112"/>
+  <dimension ref="A1:C110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -739,10 +733,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -750,10 +744,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -761,10 +755,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -772,10 +766,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -783,10 +777,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -794,10 +788,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -805,10 +799,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -816,10 +810,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -827,10 +821,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -838,10 +832,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -849,10 +843,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -860,10 +854,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -871,10 +865,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -882,10 +876,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -893,10 +887,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -904,10 +898,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -915,10 +909,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -926,10 +920,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -937,10 +931,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -948,10 +942,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -959,10 +953,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -970,10 +964,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -981,10 +975,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -992,10 +986,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1003,10 +997,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1014,10 +1008,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C27" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1025,10 +1019,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1036,10 +1030,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C29" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1047,10 +1041,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1058,10 +1052,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C31" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1069,10 +1063,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1080,10 +1074,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C33" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1094,7 +1088,7 @@
         <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1105,7 +1099,7 @@
         <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1116,7 +1110,7 @@
         <v>37</v>
       </c>
       <c r="C36" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1127,7 +1121,7 @@
         <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1138,7 +1132,7 @@
         <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1149,7 +1143,7 @@
         <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1160,7 +1154,7 @@
         <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1171,7 +1165,7 @@
         <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1182,7 +1176,7 @@
         <v>36</v>
       </c>
       <c r="C42" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1193,7 +1187,7 @@
         <v>37</v>
       </c>
       <c r="C43" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1204,7 +1198,7 @@
         <v>38</v>
       </c>
       <c r="C44" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1215,7 +1209,7 @@
         <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1226,7 +1220,7 @@
         <v>40</v>
       </c>
       <c r="C46" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1237,7 +1231,7 @@
         <v>41</v>
       </c>
       <c r="C47" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1248,7 +1242,7 @@
         <v>35</v>
       </c>
       <c r="C48" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1259,7 +1253,7 @@
         <v>36</v>
       </c>
       <c r="C49" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1270,7 +1264,7 @@
         <v>37</v>
       </c>
       <c r="C50" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1281,7 +1275,7 @@
         <v>38</v>
       </c>
       <c r="C51" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1292,7 +1286,7 @@
         <v>39</v>
       </c>
       <c r="C52" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1303,7 +1297,7 @@
         <v>40</v>
       </c>
       <c r="C53" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1314,7 +1308,7 @@
         <v>41</v>
       </c>
       <c r="C54" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1325,7 +1319,7 @@
         <v>35</v>
       </c>
       <c r="C55" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1336,7 +1330,7 @@
         <v>36</v>
       </c>
       <c r="C56" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1347,7 +1341,7 @@
         <v>37</v>
       </c>
       <c r="C57" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1358,7 +1352,7 @@
         <v>38</v>
       </c>
       <c r="C58" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1369,7 +1363,7 @@
         <v>39</v>
       </c>
       <c r="C59" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1380,7 +1374,7 @@
         <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1391,7 +1385,7 @@
         <v>41</v>
       </c>
       <c r="C61" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1399,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C62" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1410,10 +1404,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="C63" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1421,10 +1415,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="C64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1435,7 +1429,7 @@
         <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1446,7 +1440,7 @@
         <v>78</v>
       </c>
       <c r="C66" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1457,7 +1451,7 @@
         <v>80</v>
       </c>
       <c r="C67" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1468,7 +1462,7 @@
         <v>80</v>
       </c>
       <c r="C68" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1479,7 +1473,7 @@
         <v>82</v>
       </c>
       <c r="C69" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1490,7 +1484,7 @@
         <v>82</v>
       </c>
       <c r="C70" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1501,7 +1495,7 @@
         <v>84</v>
       </c>
       <c r="C71" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1512,7 +1506,7 @@
         <v>84</v>
       </c>
       <c r="C72" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1523,7 +1517,7 @@
         <v>86</v>
       </c>
       <c r="C73" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1534,7 +1528,7 @@
         <v>86</v>
       </c>
       <c r="C74" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1542,10 +1536,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C75" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1553,10 +1547,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C76" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1567,7 +1561,7 @@
         <v>78</v>
       </c>
       <c r="C77" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1578,7 +1572,7 @@
         <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1589,7 +1583,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1600,7 +1594,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1611,7 +1605,7 @@
         <v>82</v>
       </c>
       <c r="C81" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1622,7 +1616,7 @@
         <v>82</v>
       </c>
       <c r="C82" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1633,7 +1627,7 @@
         <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1644,7 +1638,7 @@
         <v>84</v>
       </c>
       <c r="C84" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1655,7 +1649,7 @@
         <v>86</v>
       </c>
       <c r="C85" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1666,7 +1660,7 @@
         <v>86</v>
       </c>
       <c r="C86" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1674,10 +1668,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C87" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1685,10 +1679,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C88" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1699,7 +1693,7 @@
         <v>102</v>
       </c>
       <c r="C89" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1710,7 +1704,7 @@
         <v>102</v>
       </c>
       <c r="C90" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1721,7 +1715,7 @@
         <v>104</v>
       </c>
       <c r="C91" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1732,7 +1726,7 @@
         <v>104</v>
       </c>
       <c r="C92" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1743,7 +1737,7 @@
         <v>106</v>
       </c>
       <c r="C93" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1754,7 +1748,7 @@
         <v>106</v>
       </c>
       <c r="C94" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1765,7 +1759,7 @@
         <v>108</v>
       </c>
       <c r="C95" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1776,7 +1770,7 @@
         <v>108</v>
       </c>
       <c r="C96" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1787,7 +1781,7 @@
         <v>110</v>
       </c>
       <c r="C97" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1798,7 +1792,7 @@
         <v>110</v>
       </c>
       <c r="C98" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1806,10 +1800,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="C99" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -1817,10 +1811,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="C100" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -1831,7 +1825,7 @@
         <v>102</v>
       </c>
       <c r="C101" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -1842,7 +1836,7 @@
         <v>102</v>
       </c>
       <c r="C102" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -1853,7 +1847,7 @@
         <v>104</v>
       </c>
       <c r="C103" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -1864,7 +1858,7 @@
         <v>104</v>
       </c>
       <c r="C104" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -1875,7 +1869,7 @@
         <v>106</v>
       </c>
       <c r="C105" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -1886,7 +1880,7 @@
         <v>106</v>
       </c>
       <c r="C106" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -1897,7 +1891,7 @@
         <v>108</v>
       </c>
       <c r="C107" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -1908,7 +1902,7 @@
         <v>108</v>
       </c>
       <c r="C108" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -1919,7 +1913,7 @@
         <v>110</v>
       </c>
       <c r="C109" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -1930,29 +1924,7 @@
         <v>110</v>
       </c>
       <c r="C110" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111" t="s">
-        <v>112</v>
-      </c>
-      <c r="B111" t="s">
-        <v>112</v>
-      </c>
-      <c r="C111" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3">
-      <c r="A112" t="s">
-        <v>113</v>
-      </c>
-      <c r="B112" t="s">
-        <v>112</v>
-      </c>
-      <c r="C112" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/sku_mapping.xlsx
+++ b/sku_mapping.xlsx
@@ -205,7 +205,7 @@
     <t>008-192-14B</t>
   </si>
   <si>
-    <t>WF-2 008-137-12</t>
+    <t>WS008-137-12C</t>
   </si>
   <si>
     <t>WS006-137-12</t>

--- a/sku_mapping.xlsx
+++ b/sku_mapping.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="126">
   <si>
     <t>原始SKU</t>
   </si>
@@ -205,7 +205,16 @@
     <t>008-192-14B</t>
   </si>
   <si>
-    <t>WS008-137-12C</t>
+    <t>L8-152-12</t>
+  </si>
+  <si>
+    <t>008-192-12-1</t>
+  </si>
+  <si>
+    <t>008-152-12-1</t>
+  </si>
+  <si>
+    <t>L8-152-12G</t>
   </si>
   <si>
     <t>WS006-137-12</t>
@@ -714,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C110"/>
+  <dimension ref="A1:C113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -733,10 +742,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -744,10 +753,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -755,10 +764,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -766,10 +775,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -777,10 +786,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -788,10 +797,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -799,10 +808,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -810,10 +819,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -821,10 +830,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -832,10 +841,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -843,10 +852,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -854,10 +863,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -865,10 +874,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -876,10 +885,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -887,10 +896,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C16" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -898,10 +907,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -909,10 +918,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -920,10 +929,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -931,10 +940,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -942,10 +951,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -953,10 +962,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -964,10 +973,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -975,10 +984,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -986,10 +995,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -997,10 +1006,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1008,10 +1017,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1019,10 +1028,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1030,10 +1039,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1041,10 +1050,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1052,10 +1061,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1063,10 +1072,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1074,10 +1083,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1088,7 +1097,7 @@
         <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1099,7 +1108,7 @@
         <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1110,7 +1119,7 @@
         <v>37</v>
       </c>
       <c r="C36" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1121,7 +1130,7 @@
         <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1132,7 +1141,7 @@
         <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1143,7 +1152,7 @@
         <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1154,7 +1163,7 @@
         <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1165,7 +1174,7 @@
         <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1176,7 +1185,7 @@
         <v>36</v>
       </c>
       <c r="C42" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1187,7 +1196,7 @@
         <v>37</v>
       </c>
       <c r="C43" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1198,7 +1207,7 @@
         <v>38</v>
       </c>
       <c r="C44" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1209,7 +1218,7 @@
         <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1220,7 +1229,7 @@
         <v>40</v>
       </c>
       <c r="C46" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1231,7 +1240,7 @@
         <v>41</v>
       </c>
       <c r="C47" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1242,7 +1251,7 @@
         <v>35</v>
       </c>
       <c r="C48" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1253,7 +1262,7 @@
         <v>36</v>
       </c>
       <c r="C49" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1264,7 +1273,7 @@
         <v>37</v>
       </c>
       <c r="C50" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1275,7 +1284,7 @@
         <v>38</v>
       </c>
       <c r="C51" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1286,7 +1295,7 @@
         <v>39</v>
       </c>
       <c r="C52" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1297,7 +1306,7 @@
         <v>40</v>
       </c>
       <c r="C53" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1308,7 +1317,7 @@
         <v>41</v>
       </c>
       <c r="C54" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1319,7 +1328,7 @@
         <v>35</v>
       </c>
       <c r="C55" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1330,7 +1339,7 @@
         <v>36</v>
       </c>
       <c r="C56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1341,7 +1350,7 @@
         <v>37</v>
       </c>
       <c r="C57" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1352,7 +1361,7 @@
         <v>38</v>
       </c>
       <c r="C58" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1363,7 +1372,7 @@
         <v>39</v>
       </c>
       <c r="C59" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1374,7 +1383,7 @@
         <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1385,7 +1394,7 @@
         <v>41</v>
       </c>
       <c r="C61" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1393,10 +1402,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C62" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1404,10 +1413,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="C63" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1415,10 +1424,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="C64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1426,10 +1435,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="C65" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1437,10 +1446,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1448,10 +1457,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1459,10 +1468,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C68" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1470,10 +1479,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C69" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1481,10 +1490,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C70" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1492,10 +1501,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C71" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1503,10 +1512,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C72" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1514,10 +1523,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C73" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1525,10 +1534,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C74" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1536,10 +1545,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C75" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1547,10 +1556,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C76" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1558,10 +1567,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C77" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1569,10 +1578,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C78" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1580,10 +1589,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C79" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1591,10 +1600,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C80" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1602,10 +1611,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C81" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1613,10 +1622,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C82" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1624,10 +1633,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C83" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1635,10 +1644,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C84" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1646,10 +1655,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C85" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1657,10 +1666,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C86" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1668,10 +1677,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="C87" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1679,10 +1688,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C88" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1690,10 +1699,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C89" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1701,10 +1710,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C90" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1712,10 +1721,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C91" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1723,10 +1732,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C92" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1734,10 +1743,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C93" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1745,10 +1754,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C94" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1756,10 +1765,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C95" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1767,10 +1776,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C96" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1778,10 +1787,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C97" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1789,10 +1798,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C98" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1800,10 +1809,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C99" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -1811,10 +1820,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="C100" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -1822,10 +1831,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="C101" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -1833,10 +1842,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C102" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -1844,10 +1853,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C103" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -1855,10 +1864,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C104" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -1866,10 +1875,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C105" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -1877,10 +1886,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C106" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -1888,10 +1897,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C107" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -1899,10 +1908,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C108" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -1910,10 +1919,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C109" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -1921,10 +1930,43 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C110" t="s">
-        <v>122</v>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" t="s">
+        <v>112</v>
+      </c>
+      <c r="B111" t="s">
+        <v>111</v>
+      </c>
+      <c r="C111" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
+        <v>113</v>
+      </c>
+      <c r="B112" t="s">
+        <v>113</v>
+      </c>
+      <c r="C112" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" t="s">
+        <v>114</v>
+      </c>
+      <c r="B113" t="s">
+        <v>113</v>
+      </c>
+      <c r="C113" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/sku_mapping.xlsx
+++ b/sku_mapping.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="125">
   <si>
     <t>原始SKU</t>
   </si>
@@ -205,16 +205,13 @@
     <t>008-192-14B</t>
   </si>
   <si>
-    <t>L8-152-12</t>
-  </si>
-  <si>
-    <t>008-192-12-1</t>
-  </si>
-  <si>
-    <t>008-152-12-1</t>
-  </si>
-  <si>
-    <t>L8-152-12G</t>
+    <t>WS008-152-12C</t>
+  </si>
+  <si>
+    <t>WS008-192-12C</t>
+  </si>
+  <si>
+    <t>WF-2 008-152-12</t>
   </si>
   <si>
     <t>WS006-137-12</t>
@@ -723,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C113"/>
+  <dimension ref="A1:C112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -742,10 +739,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -753,10 +750,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -764,10 +761,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -775,10 +772,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -786,10 +783,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -797,10 +794,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -808,10 +805,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -819,10 +816,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -830,10 +827,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -841,10 +838,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -852,10 +849,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -863,10 +860,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -874,10 +871,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -885,10 +882,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -896,10 +893,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -907,10 +904,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -918,10 +915,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -929,10 +926,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -940,10 +937,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -951,10 +948,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -962,10 +959,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -973,10 +970,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -984,10 +981,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -995,10 +992,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1006,10 +1003,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1017,10 +1014,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1028,10 +1025,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1039,10 +1036,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1050,10 +1047,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1061,10 +1058,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1072,10 +1069,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1083,10 +1080,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1097,7 +1094,7 @@
         <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1108,7 +1105,7 @@
         <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1119,7 +1116,7 @@
         <v>37</v>
       </c>
       <c r="C36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1130,7 +1127,7 @@
         <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1141,7 +1138,7 @@
         <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1152,7 +1149,7 @@
         <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1163,7 +1160,7 @@
         <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1174,7 +1171,7 @@
         <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1185,7 +1182,7 @@
         <v>36</v>
       </c>
       <c r="C42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1196,7 +1193,7 @@
         <v>37</v>
       </c>
       <c r="C43" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1207,7 +1204,7 @@
         <v>38</v>
       </c>
       <c r="C44" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1218,7 +1215,7 @@
         <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1229,7 +1226,7 @@
         <v>40</v>
       </c>
       <c r="C46" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1240,7 +1237,7 @@
         <v>41</v>
       </c>
       <c r="C47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1251,7 +1248,7 @@
         <v>35</v>
       </c>
       <c r="C48" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1262,7 +1259,7 @@
         <v>36</v>
       </c>
       <c r="C49" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1273,7 +1270,7 @@
         <v>37</v>
       </c>
       <c r="C50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1284,7 +1281,7 @@
         <v>38</v>
       </c>
       <c r="C51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1295,7 +1292,7 @@
         <v>39</v>
       </c>
       <c r="C52" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1306,7 +1303,7 @@
         <v>40</v>
       </c>
       <c r="C53" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1317,7 +1314,7 @@
         <v>41</v>
       </c>
       <c r="C54" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1328,7 +1325,7 @@
         <v>35</v>
       </c>
       <c r="C55" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1339,7 +1336,7 @@
         <v>36</v>
       </c>
       <c r="C56" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1350,7 +1347,7 @@
         <v>37</v>
       </c>
       <c r="C57" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1361,7 +1358,7 @@
         <v>38</v>
       </c>
       <c r="C58" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1372,7 +1369,7 @@
         <v>39</v>
       </c>
       <c r="C59" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1383,7 +1380,7 @@
         <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1394,7 +1391,7 @@
         <v>41</v>
       </c>
       <c r="C61" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1405,7 +1402,7 @@
         <v>38</v>
       </c>
       <c r="C62" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1416,7 +1413,7 @@
         <v>40</v>
       </c>
       <c r="C63" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1427,7 +1424,7 @@
         <v>38</v>
       </c>
       <c r="C64" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1435,7 +1432,7 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="C65" t="s">
         <v>124</v>
@@ -1446,10 +1443,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C66" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1457,10 +1454,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C67" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1468,10 +1465,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C68" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1479,10 +1476,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C69" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1490,10 +1487,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C70" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1501,10 +1498,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C71" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1512,10 +1509,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C72" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1523,10 +1520,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C73" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1534,10 +1531,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C74" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1545,10 +1542,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C75" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1556,10 +1553,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C76" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1567,10 +1564,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C77" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1578,10 +1575,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1589,10 +1586,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1600,10 +1597,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1611,10 +1608,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C81" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1622,10 +1619,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C82" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1633,10 +1630,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1644,10 +1641,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C84" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1655,10 +1652,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C85" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1666,10 +1663,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C86" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1677,10 +1674,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C87" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1688,10 +1685,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C88" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1699,10 +1696,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C89" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1710,10 +1707,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C90" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1721,10 +1718,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C91" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1732,10 +1729,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C92" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1743,10 +1740,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C93" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1754,10 +1751,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C94" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1765,10 +1762,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C95" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1776,10 +1773,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C96" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1787,10 +1784,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C97" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1798,10 +1795,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C98" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1809,10 +1806,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C99" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -1820,10 +1817,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C100" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -1831,10 +1828,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C101" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -1842,10 +1839,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C102" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -1853,10 +1850,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C103" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -1864,10 +1861,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C104" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -1875,10 +1872,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C105" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -1886,10 +1883,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C106" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -1897,10 +1894,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C107" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -1908,10 +1905,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C108" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -1919,10 +1916,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C109" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -1930,10 +1927,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C110" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -1941,10 +1938,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C111" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -1952,21 +1949,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C112" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" t="s">
-        <v>114</v>
-      </c>
-      <c r="B113" t="s">
-        <v>113</v>
-      </c>
-      <c r="C113" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/sku_mapping.xlsx
+++ b/sku_mapping.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="126">
   <si>
     <t>原始SKU</t>
   </si>
@@ -212,6 +212,9 @@
   </si>
   <si>
     <t>WF-2 008-152-12</t>
+  </si>
+  <si>
+    <t>WS008-137-12C</t>
   </si>
   <si>
     <t>WS006-137-12</t>
@@ -720,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C112"/>
+  <dimension ref="A1:C114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -739,10 +742,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -750,10 +753,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -761,10 +764,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -772,10 +775,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -783,10 +786,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -794,10 +797,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -805,10 +808,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -816,10 +819,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -827,10 +830,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -838,10 +841,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -849,10 +852,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -860,10 +863,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -871,10 +874,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -882,10 +885,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -893,10 +896,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -904,10 +907,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -915,10 +918,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -926,10 +929,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -937,10 +940,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -948,10 +951,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -959,10 +962,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -970,10 +973,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -981,10 +984,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -992,10 +995,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1003,10 +1006,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C26" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1014,10 +1017,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1025,10 +1028,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1036,10 +1039,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C29" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1047,10 +1050,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1058,10 +1061,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1069,10 +1072,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1080,10 +1083,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1094,7 +1097,7 @@
         <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1105,7 +1108,7 @@
         <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1116,7 +1119,7 @@
         <v>37</v>
       </c>
       <c r="C36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1127,7 +1130,7 @@
         <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1138,7 +1141,7 @@
         <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1149,7 +1152,7 @@
         <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1160,7 +1163,7 @@
         <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1171,7 +1174,7 @@
         <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1182,7 +1185,7 @@
         <v>36</v>
       </c>
       <c r="C42" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1193,7 +1196,7 @@
         <v>37</v>
       </c>
       <c r="C43" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1204,7 +1207,7 @@
         <v>38</v>
       </c>
       <c r="C44" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1215,7 +1218,7 @@
         <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1226,7 +1229,7 @@
         <v>40</v>
       </c>
       <c r="C46" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1237,7 +1240,7 @@
         <v>41</v>
       </c>
       <c r="C47" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1248,7 +1251,7 @@
         <v>35</v>
       </c>
       <c r="C48" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1259,7 +1262,7 @@
         <v>36</v>
       </c>
       <c r="C49" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1270,7 +1273,7 @@
         <v>37</v>
       </c>
       <c r="C50" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1281,7 +1284,7 @@
         <v>38</v>
       </c>
       <c r="C51" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1292,7 +1295,7 @@
         <v>39</v>
       </c>
       <c r="C52" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1303,7 +1306,7 @@
         <v>40</v>
       </c>
       <c r="C53" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1314,7 +1317,7 @@
         <v>41</v>
       </c>
       <c r="C54" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1325,7 +1328,7 @@
         <v>35</v>
       </c>
       <c r="C55" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1336,7 +1339,7 @@
         <v>36</v>
       </c>
       <c r="C56" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1347,7 +1350,7 @@
         <v>37</v>
       </c>
       <c r="C57" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1358,7 +1361,7 @@
         <v>38</v>
       </c>
       <c r="C58" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1369,7 +1372,7 @@
         <v>39</v>
       </c>
       <c r="C59" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1380,7 +1383,7 @@
         <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1391,7 +1394,7 @@
         <v>41</v>
       </c>
       <c r="C61" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1402,7 +1405,7 @@
         <v>38</v>
       </c>
       <c r="C62" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1413,7 +1416,7 @@
         <v>40</v>
       </c>
       <c r="C63" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1424,7 +1427,7 @@
         <v>38</v>
       </c>
       <c r="C64" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1432,7 +1435,7 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="C65" t="s">
         <v>124</v>
@@ -1440,10 +1443,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="C66" t="s">
         <v>124</v>
@@ -1451,508 +1454,530 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C69" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C70" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B71" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C71" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B72" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C72" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B73" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C73" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B74" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C74" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B75" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C75" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B76" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C76" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B77" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C77" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C78" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B79" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C79" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C80" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B81" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C81" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C82" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B83" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C83" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C84" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B85" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C85" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C86" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B87" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C87" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C88" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B89" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C89" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B90" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C90" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B91" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C91" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B92" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C92" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B93" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C93" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B94" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C94" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B95" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C95" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B96" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C96" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B97" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C97" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B98" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C98" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B99" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C99" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B100" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C100" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B101" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="C101" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="C102" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B103" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C103" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C104" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B105" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C105" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C106" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B107" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C107" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C108" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B109" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C109" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C110" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B111" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C111" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
+        <v>112</v>
+      </c>
+      <c r="B112" t="s">
+        <v>111</v>
+      </c>
+      <c r="C112" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" t="s">
         <v>113</v>
       </c>
-      <c r="B112" t="s">
-        <v>112</v>
-      </c>
-      <c r="C112" t="s">
-        <v>124</v>
+      <c r="B113" t="s">
+        <v>113</v>
+      </c>
+      <c r="C113" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" t="s">
+        <v>114</v>
+      </c>
+      <c r="B114" t="s">
+        <v>113</v>
+      </c>
+      <c r="C114" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/sku_mapping.xlsx
+++ b/sku_mapping.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="123">
   <si>
     <t>原始SKU</t>
   </si>
@@ -205,16 +205,7 @@
     <t>008-192-14B</t>
   </si>
   <si>
-    <t>WS008-152-12C</t>
-  </si>
-  <si>
-    <t>WS008-192-12C</t>
-  </si>
-  <si>
-    <t>WF-2 008-152-12</t>
-  </si>
-  <si>
-    <t>WS008-137-12C</t>
+    <t>WF-2 008-137-14</t>
   </si>
   <si>
     <t>WS006-137-12</t>
@@ -723,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C114"/>
+  <dimension ref="A1:C110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -742,10 +733,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -753,10 +744,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -764,10 +755,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -775,10 +766,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -786,10 +777,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -797,10 +788,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -808,10 +799,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -819,10 +810,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -830,10 +821,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -841,10 +832,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -852,10 +843,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C12" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -863,10 +854,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -874,10 +865,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -885,10 +876,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C15" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -896,10 +887,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C16" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -907,10 +898,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -918,10 +909,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C18" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -929,10 +920,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -940,10 +931,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C20" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -951,10 +942,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C21" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -962,10 +953,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -973,10 +964,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C23" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -984,10 +975,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C24" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -995,10 +986,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C25" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1006,10 +997,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1017,10 +1008,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C27" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1028,10 +1019,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C28" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1039,10 +1030,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1050,10 +1041,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1061,10 +1052,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1072,10 +1063,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1083,10 +1074,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1097,7 +1088,7 @@
         <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1108,7 +1099,7 @@
         <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1119,7 +1110,7 @@
         <v>37</v>
       </c>
       <c r="C36" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1130,7 +1121,7 @@
         <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1141,7 +1132,7 @@
         <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1152,7 +1143,7 @@
         <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1163,7 +1154,7 @@
         <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1174,7 +1165,7 @@
         <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1185,7 +1176,7 @@
         <v>36</v>
       </c>
       <c r="C42" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1196,7 +1187,7 @@
         <v>37</v>
       </c>
       <c r="C43" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1207,7 +1198,7 @@
         <v>38</v>
       </c>
       <c r="C44" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1218,7 +1209,7 @@
         <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1229,7 +1220,7 @@
         <v>40</v>
       </c>
       <c r="C46" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1240,7 +1231,7 @@
         <v>41</v>
       </c>
       <c r="C47" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1251,7 +1242,7 @@
         <v>35</v>
       </c>
       <c r="C48" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1262,7 +1253,7 @@
         <v>36</v>
       </c>
       <c r="C49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1273,7 +1264,7 @@
         <v>37</v>
       </c>
       <c r="C50" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1284,7 +1275,7 @@
         <v>38</v>
       </c>
       <c r="C51" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1295,7 +1286,7 @@
         <v>39</v>
       </c>
       <c r="C52" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1306,7 +1297,7 @@
         <v>40</v>
       </c>
       <c r="C53" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1317,7 +1308,7 @@
         <v>41</v>
       </c>
       <c r="C54" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1328,7 +1319,7 @@
         <v>35</v>
       </c>
       <c r="C55" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1339,7 +1330,7 @@
         <v>36</v>
       </c>
       <c r="C56" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1350,7 +1341,7 @@
         <v>37</v>
       </c>
       <c r="C57" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1361,7 +1352,7 @@
         <v>38</v>
       </c>
       <c r="C58" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1372,7 +1363,7 @@
         <v>39</v>
       </c>
       <c r="C59" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1383,7 +1374,7 @@
         <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1394,7 +1385,7 @@
         <v>41</v>
       </c>
       <c r="C61" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1402,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C62" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1413,10 +1404,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="C63" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1424,10 +1415,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="C64" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1435,549 +1426,505 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="C66" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C67" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C68" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C69" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C70" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C71" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C72" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C73" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C74" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C75" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76" t="s">
         <v>76</v>
       </c>
-      <c r="B76" t="s">
-        <v>87</v>
-      </c>
       <c r="C76" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C77" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
+        <v>79</v>
+      </c>
+      <c r="B78" t="s">
         <v>78</v>
       </c>
-      <c r="B78" t="s">
-        <v>89</v>
-      </c>
       <c r="C78" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80" t="s">
         <v>80</v>
       </c>
-      <c r="B80" t="s">
-        <v>79</v>
-      </c>
       <c r="C80" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C81" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
+        <v>83</v>
+      </c>
+      <c r="B82" t="s">
         <v>82</v>
       </c>
-      <c r="B82" t="s">
-        <v>81</v>
-      </c>
       <c r="C82" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
+        <v>85</v>
+      </c>
+      <c r="B84" t="s">
         <v>84</v>
       </c>
-      <c r="B84" t="s">
-        <v>83</v>
-      </c>
       <c r="C84" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C85" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
+        <v>87</v>
+      </c>
+      <c r="B86" t="s">
         <v>86</v>
       </c>
-      <c r="B86" t="s">
-        <v>85</v>
-      </c>
       <c r="C86" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C87" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C88" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C89" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C90" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C91" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C92" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C93" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C94" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C95" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C96" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C97" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C98" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C99" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
+        <v>101</v>
+      </c>
+      <c r="B100" t="s">
         <v>100</v>
       </c>
-      <c r="B100" t="s">
-        <v>111</v>
-      </c>
       <c r="C100" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C101" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
+        <v>103</v>
+      </c>
+      <c r="B102" t="s">
         <v>102</v>
       </c>
-      <c r="B102" t="s">
-        <v>113</v>
-      </c>
       <c r="C102" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C103" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
+        <v>105</v>
+      </c>
+      <c r="B104" t="s">
         <v>104</v>
       </c>
-      <c r="B104" t="s">
-        <v>103</v>
-      </c>
       <c r="C104" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C105" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
+        <v>107</v>
+      </c>
+      <c r="B106" t="s">
         <v>106</v>
       </c>
-      <c r="B106" t="s">
-        <v>105</v>
-      </c>
       <c r="C106" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C107" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
+        <v>109</v>
+      </c>
+      <c r="B108" t="s">
         <v>108</v>
       </c>
-      <c r="B108" t="s">
-        <v>107</v>
-      </c>
       <c r="C108" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C109" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
+        <v>111</v>
+      </c>
+      <c r="B110" t="s">
         <v>110</v>
       </c>
-      <c r="B110" t="s">
-        <v>109</v>
-      </c>
       <c r="C110" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111" t="s">
-        <v>111</v>
-      </c>
-      <c r="B111" t="s">
-        <v>111</v>
-      </c>
-      <c r="C111" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3">
-      <c r="A112" t="s">
-        <v>112</v>
-      </c>
-      <c r="B112" t="s">
-        <v>111</v>
-      </c>
-      <c r="C112" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" t="s">
-        <v>113</v>
-      </c>
-      <c r="B113" t="s">
-        <v>113</v>
-      </c>
-      <c r="C113" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3">
-      <c r="A114" t="s">
-        <v>114</v>
-      </c>
-      <c r="B114" t="s">
-        <v>113</v>
-      </c>
-      <c r="C114" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/sku_mapping.xlsx
+++ b/sku_mapping.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="124">
   <si>
     <t>原始SKU</t>
   </si>
@@ -206,6 +206,9 @@
   </si>
   <si>
     <t>WF-2 008-137-14</t>
+  </si>
+  <si>
+    <t>WS008-152-12C</t>
   </si>
   <si>
     <t>WS006-137-12</t>
@@ -714,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C110"/>
+  <dimension ref="A1:C111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -733,10 +736,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -744,10 +747,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -755,10 +758,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -766,10 +769,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -777,10 +780,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -788,10 +791,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -799,10 +802,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -810,10 +813,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -821,10 +824,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -832,10 +835,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -843,10 +846,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -854,10 +857,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -865,10 +868,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -876,10 +879,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -887,10 +890,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -898,10 +901,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -909,10 +912,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -920,10 +923,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C19" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -931,10 +934,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -942,10 +945,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -953,10 +956,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -964,10 +967,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -975,10 +978,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -986,10 +989,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -997,10 +1000,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1008,10 +1011,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1019,10 +1022,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1030,10 +1033,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1041,10 +1044,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1052,10 +1055,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1063,10 +1066,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1074,10 +1077,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1088,7 +1091,7 @@
         <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1099,7 +1102,7 @@
         <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1110,7 +1113,7 @@
         <v>37</v>
       </c>
       <c r="C36" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1121,7 +1124,7 @@
         <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1132,7 +1135,7 @@
         <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1143,7 +1146,7 @@
         <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1154,7 +1157,7 @@
         <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1165,7 +1168,7 @@
         <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1176,7 +1179,7 @@
         <v>36</v>
       </c>
       <c r="C42" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1187,7 +1190,7 @@
         <v>37</v>
       </c>
       <c r="C43" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1198,7 +1201,7 @@
         <v>38</v>
       </c>
       <c r="C44" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1209,7 +1212,7 @@
         <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1220,7 +1223,7 @@
         <v>40</v>
       </c>
       <c r="C46" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1231,7 +1234,7 @@
         <v>41</v>
       </c>
       <c r="C47" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1242,7 +1245,7 @@
         <v>35</v>
       </c>
       <c r="C48" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1253,7 +1256,7 @@
         <v>36</v>
       </c>
       <c r="C49" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1264,7 +1267,7 @@
         <v>37</v>
       </c>
       <c r="C50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1275,7 +1278,7 @@
         <v>38</v>
       </c>
       <c r="C51" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1286,7 +1289,7 @@
         <v>39</v>
       </c>
       <c r="C52" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1297,7 +1300,7 @@
         <v>40</v>
       </c>
       <c r="C53" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1308,7 +1311,7 @@
         <v>41</v>
       </c>
       <c r="C54" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1319,7 +1322,7 @@
         <v>35</v>
       </c>
       <c r="C55" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1330,7 +1333,7 @@
         <v>36</v>
       </c>
       <c r="C56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1341,7 +1344,7 @@
         <v>37</v>
       </c>
       <c r="C57" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1352,7 +1355,7 @@
         <v>38</v>
       </c>
       <c r="C58" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1363,7 +1366,7 @@
         <v>39</v>
       </c>
       <c r="C59" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1374,7 +1377,7 @@
         <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1385,7 +1388,7 @@
         <v>41</v>
       </c>
       <c r="C61" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1396,7 +1399,7 @@
         <v>37</v>
       </c>
       <c r="C62" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1404,7 +1407,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="C63" t="s">
         <v>122</v>
@@ -1415,10 +1418,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C64" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1426,10 +1429,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C65" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1437,10 +1440,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1448,10 +1451,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1459,10 +1462,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C68" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1470,10 +1473,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C69" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1481,10 +1484,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C70" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1492,10 +1495,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C71" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1503,10 +1506,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C72" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1514,10 +1517,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C73" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1525,10 +1528,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C74" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1536,10 +1539,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C75" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1547,10 +1550,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C76" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1558,10 +1561,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C77" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1569,10 +1572,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C78" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1580,10 +1583,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C79" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1591,10 +1594,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C80" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1602,10 +1605,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C81" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1613,10 +1616,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C82" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1624,10 +1627,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C83" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1635,10 +1638,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C84" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1646,10 +1649,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C85" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1657,10 +1660,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C86" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1668,10 +1671,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="C87" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1679,10 +1682,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C88" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1690,10 +1693,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C89" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1701,10 +1704,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C90" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1712,10 +1715,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C91" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1723,10 +1726,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C92" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1734,10 +1737,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C93" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1745,10 +1748,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C94" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1756,10 +1759,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C95" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1767,10 +1770,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C96" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1778,10 +1781,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C97" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1789,10 +1792,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C98" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1800,10 +1803,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C99" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -1811,10 +1814,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C100" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -1822,10 +1825,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C101" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -1833,10 +1836,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C102" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -1844,10 +1847,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C103" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -1855,10 +1858,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C104" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -1866,10 +1869,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C105" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -1877,10 +1880,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C106" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -1888,10 +1891,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C107" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -1899,10 +1902,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C108" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -1910,10 +1913,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C109" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -1921,10 +1924,21 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C110" t="s">
-        <v>122</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" t="s">
+        <v>112</v>
+      </c>
+      <c r="B111" t="s">
+        <v>111</v>
+      </c>
+      <c r="C111" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/sku_mapping.xlsx
+++ b/sku_mapping.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="125">
   <si>
     <t>原始SKU</t>
   </si>
@@ -205,10 +205,13 @@
     <t>008-192-14B</t>
   </si>
   <si>
-    <t>WF-2 008-137-14</t>
-  </si>
-  <si>
-    <t>WS008-152-12C</t>
+    <t>WS008-192-12C</t>
+  </si>
+  <si>
+    <t>WF-2 008-152-12</t>
+  </si>
+  <si>
+    <t>WS008-137-12C</t>
   </si>
   <si>
     <t>WS006-137-12</t>
@@ -717,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C111"/>
+  <dimension ref="A1:C112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -736,10 +739,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -747,10 +750,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -758,10 +761,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -769,10 +772,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -780,10 +783,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -791,10 +794,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -802,10 +805,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -813,10 +816,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -824,10 +827,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -835,10 +838,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -846,10 +849,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -857,10 +860,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -868,10 +871,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -879,10 +882,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -890,10 +893,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -901,10 +904,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -912,10 +915,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -923,10 +926,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -934,10 +937,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -945,10 +948,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -956,10 +959,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -967,10 +970,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -978,10 +981,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -989,10 +992,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C25" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1000,10 +1003,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1011,10 +1014,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1022,10 +1025,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1033,10 +1036,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1044,10 +1047,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1055,10 +1058,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1066,10 +1069,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1077,10 +1080,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1091,7 +1094,7 @@
         <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1102,7 +1105,7 @@
         <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1113,7 +1116,7 @@
         <v>37</v>
       </c>
       <c r="C36" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1124,7 +1127,7 @@
         <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1135,7 +1138,7 @@
         <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1146,7 +1149,7 @@
         <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1157,7 +1160,7 @@
         <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1168,7 +1171,7 @@
         <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1179,7 +1182,7 @@
         <v>36</v>
       </c>
       <c r="C42" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1190,7 +1193,7 @@
         <v>37</v>
       </c>
       <c r="C43" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1201,7 +1204,7 @@
         <v>38</v>
       </c>
       <c r="C44" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1212,7 +1215,7 @@
         <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1223,7 +1226,7 @@
         <v>40</v>
       </c>
       <c r="C46" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1234,7 +1237,7 @@
         <v>41</v>
       </c>
       <c r="C47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1245,7 +1248,7 @@
         <v>35</v>
       </c>
       <c r="C48" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1256,7 +1259,7 @@
         <v>36</v>
       </c>
       <c r="C49" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1267,7 +1270,7 @@
         <v>37</v>
       </c>
       <c r="C50" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1278,7 +1281,7 @@
         <v>38</v>
       </c>
       <c r="C51" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1289,7 +1292,7 @@
         <v>39</v>
       </c>
       <c r="C52" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1300,7 +1303,7 @@
         <v>40</v>
       </c>
       <c r="C53" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1311,7 +1314,7 @@
         <v>41</v>
       </c>
       <c r="C54" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1322,7 +1325,7 @@
         <v>35</v>
       </c>
       <c r="C55" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1333,7 +1336,7 @@
         <v>36</v>
       </c>
       <c r="C56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1344,7 +1347,7 @@
         <v>37</v>
       </c>
       <c r="C57" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1355,7 +1358,7 @@
         <v>38</v>
       </c>
       <c r="C58" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1366,7 +1369,7 @@
         <v>39</v>
       </c>
       <c r="C59" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1377,7 +1380,7 @@
         <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1388,7 +1391,7 @@
         <v>41</v>
       </c>
       <c r="C61" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1396,10 +1399,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C62" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1410,7 +1413,7 @@
         <v>38</v>
       </c>
       <c r="C63" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1418,7 +1421,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="C64" t="s">
         <v>123</v>
@@ -1429,10 +1432,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1440,10 +1443,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C66" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1451,10 +1454,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C67" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1462,10 +1465,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C68" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1473,10 +1476,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C69" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1484,10 +1487,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C70" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1495,10 +1498,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C71" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1506,10 +1509,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C72" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1517,10 +1520,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C73" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1528,10 +1531,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C74" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1539,10 +1542,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C75" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1550,10 +1553,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C76" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1561,10 +1564,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C77" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1572,10 +1575,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1583,10 +1586,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1594,10 +1597,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1605,10 +1608,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C81" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1616,10 +1619,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C82" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1627,10 +1630,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1638,10 +1641,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C84" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1649,10 +1652,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C85" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1660,10 +1663,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C86" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1671,10 +1674,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C87" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1682,10 +1685,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C88" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1693,10 +1696,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C89" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1704,10 +1707,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C90" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1715,10 +1718,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C91" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1726,10 +1729,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C92" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1737,10 +1740,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C93" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1748,10 +1751,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C94" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1759,10 +1762,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C95" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1770,10 +1773,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C96" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1781,10 +1784,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C97" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1792,10 +1795,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C98" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1803,10 +1806,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C99" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -1814,10 +1817,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="C100" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -1825,10 +1828,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C101" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -1836,10 +1839,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C102" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -1847,10 +1850,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C103" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -1858,10 +1861,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C104" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -1869,10 +1872,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C105" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -1880,10 +1883,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C106" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -1891,10 +1894,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C107" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -1902,10 +1905,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C108" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -1913,10 +1916,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C109" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -1924,10 +1927,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C110" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -1935,10 +1938,21 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C111" t="s">
-        <v>123</v>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
+        <v>113</v>
+      </c>
+      <c r="B112" t="s">
+        <v>112</v>
+      </c>
+      <c r="C112" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
